--- a/trainingwork0/答案/result/problem1_predictions.xlsx
+++ b/trainingwork0/答案/result/problem1_predictions.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3224</v>
+        <v>0.3208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3874</v>
+        <v>0.4115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2524000108242035</v>
+        <v>0.2892000079154968</v>
       </c>
       <c r="F2" t="n">
         <v>0.4917</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3414</v>
+        <v>0.3588</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3212</v>
+        <v>0.3206</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3847</v>
+        <v>0.4081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2515000104904175</v>
+        <v>0.2829000055789948</v>
       </c>
       <c r="F3" t="n">
         <v>0.4982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3403</v>
+        <v>0.3559</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3231</v>
+        <v>0.3218</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3875</v>
+        <v>0.4128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.252700001001358</v>
+        <v>0.2840000092983246</v>
       </c>
       <c r="F4" t="n">
         <v>0.5077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3431</v>
+        <v>0.3592</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3506</v>
+        <v>0.3488</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4433</v>
+        <v>0.4665</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2967999875545502</v>
+        <v>0.3325999975204468</v>
       </c>
       <c r="F5" t="n">
         <v>0.5013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3855</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4577</v>
+        <v>0.496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.300900012254715</v>
+        <v>0.3411999940872192</v>
       </c>
       <c r="F6" t="n">
         <v>0.5074</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3922</v>
+        <v>0.4156</v>
       </c>
     </row>
     <row r="7">
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2954</v>
+        <v>0.2888</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4118</v>
+        <v>0.4374</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2427999973297119</v>
+        <v>0.3089999854564667</v>
       </c>
       <c r="F7" t="n">
         <v>0.469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3401</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="8">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3579</v>
+        <v>0.3497</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4406</v>
+        <v>0.4685</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2987000048160553</v>
+        <v>0.3467999994754791</v>
       </c>
       <c r="F8" t="n">
         <v>0.5285</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3892</v>
+        <v>0.4101</v>
       </c>
     </row>
     <row r="9">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3511</v>
+        <v>0.3419</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4503</v>
+        <v>0.502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2906000018119812</v>
+        <v>0.3309000134468079</v>
       </c>
       <c r="F9" t="n">
         <v>0.4927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.386</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="10">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3215</v>
+        <v>0.3183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3948</v>
+        <v>0.4416</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2563000023365021</v>
+        <v>0.2949000000953674</v>
       </c>
       <c r="F10" t="n">
         <v>0.5243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3483</v>
+        <v>0.3747</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3218</v>
+        <v>0.318</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3641</v>
+        <v>0.3924</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2531000077724457</v>
+        <v>0.287200003862381</v>
       </c>
       <c r="F11" t="n">
         <v>0.5212</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3344</v>
+        <v>0.3526</v>
       </c>
     </row>
     <row r="12">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3243</v>
+        <v>0.3212</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3739</v>
+        <v>0.4028</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2496999949216843</v>
+        <v>0.2856000065803528</v>
       </c>
       <c r="F12" t="n">
         <v>0.5395</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3396</v>
+        <v>0.3585</v>
       </c>
     </row>
     <row r="13">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3231</v>
+        <v>0.3213</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3923</v>
+        <v>0.4212</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2522000074386597</v>
+        <v>0.289000004529953</v>
       </c>
       <c r="F13" t="n">
         <v>0.5061</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3448</v>
+        <v>0.3639</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.3178</v>
+        <v>0.3186</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3801</v>
+        <v>0.4095</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2642999887466431</v>
+        <v>0.2764999866485596</v>
       </c>
       <c r="F14" t="n">
         <v>0.4819</v>
       </c>
       <c r="G14" t="n">
-        <v>0.34</v>
+        <v>0.3524</v>
       </c>
     </row>
     <row r="15">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3971</v>
+        <v>0.4234</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2939999997615814</v>
+        <v>0.3224999904632568</v>
       </c>
       <c r="F15" t="n">
         <v>0.4827</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3597</v>
+        <v>0.3761</v>
       </c>
     </row>
     <row r="16">
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.3338</v>
+        <v>0.3319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4469</v>
+        <v>0.488</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3034000098705292</v>
+        <v>0.3364000022411346</v>
       </c>
       <c r="F16" t="n">
         <v>0.5107</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3858</v>
+        <v>0.4086</v>
       </c>
     </row>
     <row r="17">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3462</v>
+        <v>0.3428</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4438</v>
+        <v>0.4902</v>
       </c>
       <c r="E17" t="n">
-        <v>0.300900012254715</v>
+        <v>0.3388999998569489</v>
       </c>
       <c r="F17" t="n">
         <v>0.5047</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3862</v>
+        <v>0.4123</v>
       </c>
     </row>
     <row r="18">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3504</v>
+        <v>0.3433</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4466</v>
+        <v>0.496</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3032000064849854</v>
+        <v>0.3411999940872192</v>
       </c>
       <c r="F18" t="n">
         <v>0.4815</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3871</v>
+        <v>0.4134</v>
       </c>
     </row>
     <row r="19">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3231</v>
+        <v>0.3208</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3762</v>
+        <v>0.4166</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2606000006198883</v>
+        <v>0.2967999875545502</v>
       </c>
       <c r="F19" t="n">
         <v>0.5343</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3431</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="20">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.3229</v>
+        <v>0.3208</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4004</v>
+        <v>0.4404</v>
       </c>
       <c r="E20" t="n">
-        <v>0.269899994134903</v>
+        <v>0.3084999918937683</v>
       </c>
       <c r="F20" t="n">
         <v>0.4989</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3528</v>
+        <v>0.3771</v>
       </c>
     </row>
     <row r="21">
@@ -990,19 +990,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.3051</v>
+        <v>0.3091</v>
       </c>
       <c r="D21" t="n">
-        <v>0.341</v>
+        <v>0.3673</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2556999921798706</v>
+        <v>0.2664999961853027</v>
       </c>
       <c r="F21" t="n">
         <v>0.3769</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3089</v>
+        <v>0.3212</v>
       </c>
     </row>
     <row r="22">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3208</v>
+        <v>0.3212</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3488</v>
+        <v>0.3771</v>
       </c>
       <c r="E22" t="n">
-        <v>0.261599987745285</v>
+        <v>0.270799994468689</v>
       </c>
       <c r="F22" t="n">
         <v>0.5086000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3292</v>
+        <v>0.3408</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3194</v>
+        <v>0.3202</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3505</v>
+        <v>0.3788</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2621000111103058</v>
+        <v>0.2703000009059906</v>
       </c>
       <c r="F23" t="n">
         <v>0.5042</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3293</v>
+        <v>0.3407</v>
       </c>
     </row>
     <row r="24">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3191</v>
+        <v>0.3189</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3427</v>
+        <v>0.3689</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2626999914646149</v>
+        <v>0.2693000137805939</v>
       </c>
       <c r="F24" t="n">
         <v>0.4962</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3255</v>
+        <v>0.3355</v>
       </c>
     </row>
     <row r="25">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3188</v>
+        <v>0.3192</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3422</v>
+        <v>0.3716</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2635000050067902</v>
+        <v>0.2700999975204468</v>
       </c>
       <c r="F25" t="n">
         <v>0.5062</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3263</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="26">
@@ -1125,19 +1125,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1936</v>
+        <v>0.1934</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3054</v>
+        <v>0.3569</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2143999934196472</v>
+        <v>0.3037999868392944</v>
       </c>
       <c r="F26" t="n">
         <v>0.4188</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2585</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="27">
@@ -1152,19 +1152,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.235</v>
+        <v>0.2276</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3291</v>
+        <v>0.3972</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2206999957561493</v>
+        <v>0.3169000148773193</v>
       </c>
       <c r="F27" t="n">
         <v>0.2902</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2689</v>
+        <v>0.3228</v>
       </c>
     </row>
     <row r="28">
@@ -1179,19 +1179,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.2374</v>
+        <v>0.2305</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3276</v>
+        <v>0.3965</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2278999984264374</v>
+        <v>0.3217999935150146</v>
       </c>
       <c r="F28" t="n">
         <v>0.2713</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2693</v>
+        <v>0.3232</v>
       </c>
     </row>
     <row r="29">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3562</v>
+        <v>0.3496</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4454</v>
+        <v>0.499</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3023000061511993</v>
+        <v>0.3352999985218048</v>
       </c>
       <c r="F29" t="n">
         <v>0.543</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3931</v>
+        <v>0.4195</v>
       </c>
     </row>
     <row r="30">
@@ -1233,19 +1233,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.2082</v>
+        <v>0.2043</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3528</v>
+        <v>0.4123</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2294999957084656</v>
+        <v>0.3179999887943268</v>
       </c>
       <c r="F30" t="n">
         <v>0.4075</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2852</v>
+        <v>0.3339</v>
       </c>
     </row>
     <row r="31">
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1964</v>
+        <v>0.1932</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3244</v>
+        <v>0.384</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2161000072956085</v>
+        <v>0.3120000064373016</v>
       </c>
       <c r="F31" t="n">
         <v>0.4073</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2665</v>
+        <v>0.3182</v>
       </c>
     </row>
     <row r="32">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2263</v>
+        <v>0.2251</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3161</v>
+        <v>0.3657</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2494000047445297</v>
+        <v>0.3274999856948853</v>
       </c>
       <c r="F32" t="n">
         <v>0.1766</v>
       </c>
       <c r="G32" t="n">
-        <v>0.26</v>
+        <v>0.3034</v>
       </c>
     </row>
     <row r="33">
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3427</v>
+        <v>0.3411</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3396</v>
+        <v>0.3713</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3086000084877014</v>
+        <v>0.3154999911785126</v>
       </c>
       <c r="F33" t="n">
         <v>0.5238</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3461</v>
+        <v>0.3594</v>
       </c>
     </row>
     <row r="34">
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.3458</v>
+        <v>0.3402</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3421</v>
+        <v>0.3779</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2940999865531921</v>
+        <v>0.3059999942779541</v>
       </c>
       <c r="F34" t="n">
         <v>0.5181</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3431</v>
+        <v>0.3581</v>
       </c>
     </row>
     <row r="35">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.3468</v>
+        <v>0.3419</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3782</v>
+        <v>0.4248</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2944999933242798</v>
+        <v>0.3221000134944916</v>
       </c>
       <c r="F35" t="n">
         <v>0.5037</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3571</v>
+        <v>0.3809</v>
       </c>
     </row>
     <row r="36">
@@ -1395,19 +1395,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.3443</v>
+        <v>0.3426</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3623</v>
+        <v>0.389</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2849999964237213</v>
+        <v>0.3106000125408173</v>
       </c>
       <c r="F36" t="n">
         <v>0.5185</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3484</v>
+        <v>0.3645</v>
       </c>
     </row>
     <row r="37">
@@ -1422,19 +1422,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.3431</v>
+        <v>0.3404</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3636</v>
+        <v>0.3923</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2856999933719635</v>
+        <v>0.2944999933242798</v>
       </c>
       <c r="F37" t="n">
         <v>0.4885</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3462</v>
+        <v>0.3573</v>
       </c>
     </row>
     <row r="38">
@@ -1449,19 +1449,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.2233</v>
+        <v>0.226</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2222</v>
+        <v>0.2186</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2356999963521957</v>
+        <v>0.2592000067234039</v>
       </c>
       <c r="F38" t="n">
         <v>0.2267</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2206</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="39">
@@ -1476,19 +1476,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.2185</v>
+        <v>0.2208</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2494</v>
+        <v>0.2458</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2346999943256378</v>
+        <v>0.2500999867916107</v>
       </c>
       <c r="F39" t="n">
         <v>0.2397</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2316</v>
+        <v>0.2355</v>
       </c>
     </row>
     <row r="40">
@@ -1503,19 +1503,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.2074</v>
+        <v>0.2059</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2594</v>
+        <v>0.2558</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2257000058889389</v>
+        <v>0.25</v>
       </c>
       <c r="F40" t="n">
         <v>0.2207</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2286</v>
+        <v>0.2342</v>
       </c>
     </row>
     <row r="41">
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.4591</v>
+        <v>0.4546</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4316</v>
+        <v>0.4473</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5601999759674072</v>
+        <v>0.5694000124931335</v>
       </c>
       <c r="F41" t="n">
         <v>0.3925</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4764</v>
+        <v>0.4882</v>
       </c>
     </row>
     <row r="42">
@@ -1557,19 +1557,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5223</v>
+        <v>0.5107</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4722</v>
+        <v>0.4565</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5963000059127808</v>
+        <v>0.5971000194549561</v>
       </c>
       <c r="F42" t="n">
         <v>0.529</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5314</v>
+        <v>0.5261</v>
       </c>
     </row>
     <row r="43">
@@ -1584,19 +1584,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4991</v>
+        <v>0.4901</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4741</v>
+        <v>0.4468</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5813999772071838</v>
+        <v>0.5799000263214111</v>
       </c>
       <c r="F43" t="n">
         <v>0.4543</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5155</v>
+        <v>0.5052</v>
       </c>
     </row>
     <row r="44">
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4914</v>
+        <v>0.4771</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4371</v>
+        <v>0.4275</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5990999937057495</v>
+        <v>0.5978000164031982</v>
       </c>
       <c r="F44" t="n">
         <v>0.4018</v>
       </c>
       <c r="G44" t="n">
-        <v>0.499</v>
+        <v>0.4959</v>
       </c>
     </row>
     <row r="45">
@@ -1638,19 +1638,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.5006</v>
+        <v>0.4891</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3823</v>
+        <v>0.3819</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5993999838829041</v>
+        <v>0.5982999801635742</v>
       </c>
       <c r="F45" t="n">
         <v>0.423</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4804</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="46">
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.2322</v>
+        <v>0.234</v>
       </c>
       <c r="D46" t="n">
-        <v>0.239</v>
+        <v>0.2324</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2574000060558319</v>
+        <v>0.2533000111579895</v>
       </c>
       <c r="F46" t="n">
         <v>0.3099</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2435</v>
+        <v>0.2406</v>
       </c>
     </row>
     <row r="47">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.2275</v>
+        <v>0.2282</v>
       </c>
       <c r="D47" t="n">
-        <v>0.208</v>
+        <v>0.1997</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2329999953508377</v>
+        <v>0.2540000081062317</v>
       </c>
       <c r="F47" t="n">
         <v>0.2991</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2212</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="48">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.2263</v>
+        <v>0.2282</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2023</v>
+        <v>0.1913</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2241999953985214</v>
+        <v>0.2506999969482422</v>
       </c>
       <c r="F48" t="n">
         <v>0.1884</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2062</v>
+        <v>0.2116</v>
       </c>
     </row>
     <row r="49">
@@ -1746,19 +1746,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.2262</v>
+        <v>0.2269</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2054</v>
+        <v>0.1958</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2222999930381775</v>
+        <v>0.2493000030517578</v>
       </c>
       <c r="F49" t="n">
         <v>0.1588</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2043</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="50">
@@ -1773,19 +1773,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.2085</v>
+        <v>0.2097</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2698</v>
+        <v>0.2932</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2524999976158142</v>
+        <v>0.2869000136852264</v>
       </c>
       <c r="F50" t="n">
         <v>0.1698</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2368</v>
+        <v>0.2575</v>
       </c>
     </row>
     <row r="51">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.2099</v>
+        <v>0.209</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4736</v>
+        <v>0.503</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2594999969005585</v>
+        <v>0.294299989938736</v>
       </c>
       <c r="F51" t="n">
         <v>0.1678</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3237</v>
+        <v>0.3415</v>
       </c>
     </row>
     <row r="52">
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.2069</v>
+        <v>0.2081</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4737</v>
+        <v>0.5017</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2635999917984009</v>
+        <v>0.2917999923229218</v>
       </c>
       <c r="F52" t="n">
         <v>0.1968</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3268</v>
+        <v>0.3426</v>
       </c>
     </row>
     <row r="53">
@@ -1854,19 +1854,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.2395</v>
+        <v>0.2404</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2463</v>
+        <v>0.235</v>
       </c>
       <c r="E53" t="n">
-        <v>0.225600004196167</v>
+        <v>0.2556999921798706</v>
       </c>
       <c r="F53" t="n">
         <v>0.1648</v>
       </c>
       <c r="G53" t="n">
-        <v>0.226</v>
+        <v>0.2311</v>
       </c>
     </row>
     <row r="54">
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.205</v>
+        <v>0.2043</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2249</v>
+        <v>0.2205</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2132000029087067</v>
+        <v>0.2448000013828278</v>
       </c>
       <c r="F54" t="n">
         <v>0.1602</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2047</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="55">
@@ -1908,19 +1908,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2068</v>
+        <v>0.2064</v>
       </c>
       <c r="D55" t="n">
-        <v>0.246</v>
+        <v>0.2432</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2108000069856644</v>
+        <v>0.2396000027656555</v>
       </c>
       <c r="F55" t="n">
         <v>0.1734</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2143</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="56">
@@ -1935,19 +1935,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.2055</v>
+        <v>0.2066</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2356</v>
+        <v>0.2326</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2101999968290329</v>
+        <v>0.241799995303154</v>
       </c>
       <c r="F56" t="n">
         <v>0.1841</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2104</v>
+        <v>0.2194</v>
       </c>
     </row>
     <row r="57">
@@ -1962,19 +1962,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.2021</v>
+        <v>0.2031</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2527</v>
+        <v>0.2542</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2079000025987625</v>
+        <v>0.2342000007629395</v>
       </c>
       <c r="F57" t="n">
         <v>0.1512</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2132</v>
+        <v>0.2216</v>
       </c>
     </row>
     <row r="58">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.2006</v>
+        <v>0.2032</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2609</v>
+        <v>0.2719</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2178999930620193</v>
+        <v>0.248199999332428</v>
       </c>
       <c r="F58" t="n">
         <v>0.1826</v>
       </c>
       <c r="G58" t="n">
-        <v>0.222</v>
+        <v>0.2359</v>
       </c>
     </row>
     <row r="59">
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2011</v>
+        <v>0.2039</v>
       </c>
       <c r="D59" t="n">
-        <v>0.241</v>
+        <v>0.2521</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2124000042676926</v>
+        <v>0.2335000038146973</v>
       </c>
       <c r="F59" t="n">
         <v>0.2282</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2162</v>
+        <v>0.2275</v>
       </c>
     </row>
     <row r="60">
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2023</v>
+        <v>0.2044</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2465</v>
+        <v>0.2632</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2197999954223633</v>
+        <v>0.2441000044345856</v>
       </c>
       <c r="F60" t="n">
         <v>0.1874</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2174</v>
+        <v>0.2319</v>
       </c>
     </row>
     <row r="61">
@@ -2070,19 +2070,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.1996</v>
+        <v>0.2032</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2594</v>
+        <v>0.2705</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2205999940633774</v>
+        <v>0.2422000020742416</v>
       </c>
       <c r="F61" t="n">
         <v>0.2183</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2251</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="62">
@@ -2097,19 +2097,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.2069</v>
+        <v>0.2088</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3557</v>
+        <v>0.3761</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2542999982833862</v>
+        <v>0.2892000079154968</v>
       </c>
       <c r="F62" t="n">
         <v>0.2534</v>
       </c>
       <c r="G62" t="n">
-        <v>0.28</v>
+        <v>0.2977</v>
       </c>
     </row>
     <row r="63">
@@ -2124,19 +2124,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.203</v>
+        <v>0.2052</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4706</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2545999884605408</v>
+        <v>0.2894999980926514</v>
       </c>
       <c r="F63" t="n">
         <v>0.2327</v>
       </c>
       <c r="G63" t="n">
-        <v>0.325</v>
+        <v>0.3438</v>
       </c>
     </row>
     <row r="64">
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.2016</v>
+        <v>0.2027</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4505</v>
+        <v>0.4802</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2515000104904175</v>
+        <v>0.2860000133514404</v>
       </c>
       <c r="F64" t="n">
         <v>0.2665</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3184</v>
+        <v>0.3371</v>
       </c>
     </row>
     <row r="65">
@@ -2178,19 +2178,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.1955</v>
+        <v>0.198</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4675</v>
+        <v>0.4881</v>
       </c>
       <c r="E65" t="n">
-        <v>0.251800000667572</v>
+        <v>0.286300003528595</v>
       </c>
       <c r="F65" t="n">
         <v>0.2092</v>
       </c>
       <c r="G65" t="n">
-        <v>0.319</v>
+        <v>0.3341</v>
       </c>
     </row>
     <row r="66">
@@ -2205,19 +2205,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.2017</v>
+        <v>0.2006</v>
       </c>
       <c r="D66" t="n">
-        <v>0.254</v>
+        <v>0.2665</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2208999991416931</v>
+        <v>0.2436999976634979</v>
       </c>
       <c r="F66" t="n">
         <v>0.2423</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2255</v>
+        <v>0.2369</v>
       </c>
     </row>
     <row r="67">
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.2248</v>
+        <v>0.2256</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2592</v>
+        <v>0.2696</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2216999977827072</v>
+        <v>0.2445999979972839</v>
       </c>
       <c r="F67" t="n">
         <v>0.2888</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2376</v>
+        <v>0.2484</v>
       </c>
     </row>
     <row r="68">
@@ -2259,19 +2259,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.2238</v>
+        <v>0.2243</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2792</v>
+        <v>0.2826</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2290000021457672</v>
+        <v>0.251800000667572</v>
       </c>
       <c r="F68" t="n">
         <v>0.3093</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2496</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="69">
@@ -2286,19 +2286,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.2301</v>
+        <v>0.2326</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2984</v>
+        <v>0.3038</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2509999871253967</v>
+        <v>0.2755999863147736</v>
       </c>
       <c r="F69" t="n">
         <v>0.348</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2691</v>
+        <v>0.2789</v>
       </c>
     </row>
     <row r="70">
@@ -2313,19 +2313,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.4471</v>
+        <v>0.441</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4926</v>
+        <v>0.5275</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4837999939918518</v>
+        <v>0.5019000172615051</v>
       </c>
       <c r="F70" t="n">
         <v>0.553</v>
       </c>
       <c r="G70" t="n">
-        <v>0.49</v>
+        <v>0.5081</v>
       </c>
     </row>
     <row r="71">
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.3614</v>
+        <v>0.3585</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4095</v>
+        <v>0.4423</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4284999966621399</v>
+        <v>0.4379999935626984</v>
       </c>
       <c r="F71" t="n">
         <v>0.3756</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4027</v>
+        <v>0.4187</v>
       </c>
     </row>
     <row r="72">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.4556</v>
+        <v>0.4471</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4545</v>
+        <v>0.4987</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4704000055789948</v>
+        <v>0.4724999964237213</v>
       </c>
       <c r="F72" t="n">
         <v>0.3513</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4545</v>
+        <v>0.4708</v>
       </c>
     </row>
     <row r="73">
@@ -2394,19 +2394,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.4495</v>
+        <v>0.444</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4698</v>
+        <v>0.4985</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4704000055789948</v>
       </c>
       <c r="F73" t="n">
         <v>0.3523</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4563</v>
+        <v>0.4694</v>
       </c>
     </row>
     <row r="74">
@@ -2421,19 +2421,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.2226</v>
+        <v>0.2268</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3316</v>
+        <v>0.3402</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2362000048160553</v>
+        <v>0.2800000011920929</v>
       </c>
       <c r="F74" t="n">
         <v>0.321</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2743</v>
+        <v>0.2908</v>
       </c>
     </row>
     <row r="75">
@@ -2448,19 +2448,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.2185</v>
+        <v>0.2192</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2745</v>
+        <v>0.2809</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2081999927759171</v>
+        <v>0.2289000004529953</v>
       </c>
       <c r="F75" t="n">
         <v>0.3041</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2397</v>
+        <v>0.2475</v>
       </c>
     </row>
     <row r="76">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.2225</v>
+        <v>0.2262</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3036</v>
+        <v>0.3225</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2345000058412552</v>
+        <v>0.2671999931335449</v>
       </c>
       <c r="F76" t="n">
         <v>0.3366</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2635</v>
+        <v>0.2809</v>
       </c>
     </row>
     <row r="77">
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.5103</v>
+        <v>0.4989</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4532</v>
+        <v>0.4566</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5072000026702881</v>
+        <v>0.5152999758720398</v>
       </c>
       <c r="F77" t="n">
         <v>0.2543</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4697</v>
+        <v>0.4722</v>
       </c>
     </row>
     <row r="78">
@@ -2529,19 +2529,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.5131</v>
+        <v>0.5031</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4548</v>
+        <v>0.4656</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5206999778747559</v>
+        <v>0.5315999984741211</v>
       </c>
       <c r="F78" t="n">
         <v>0.2114</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4713</v>
+        <v>0.4783</v>
       </c>
     </row>
     <row r="79">
@@ -2556,19 +2556,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.2339</v>
+        <v>0.23</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2845</v>
+        <v>0.2882</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2220000028610229</v>
+        <v>0.2425999939441681</v>
       </c>
       <c r="F79" t="n">
         <v>0.3078</v>
       </c>
       <c r="G79" t="n">
-        <v>0.252</v>
+        <v>0.2577</v>
       </c>
     </row>
     <row r="80">
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.2191</v>
+        <v>0.2177</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2551</v>
+        <v>0.2546</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2037999927997589</v>
+        <v>0.2245000004768372</v>
       </c>
       <c r="F80" t="n">
         <v>0.262</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2268</v>
+        <v>0.2317</v>
       </c>
     </row>
     <row r="81">
@@ -2610,19 +2610,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.465</v>
+        <v>0.4535</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4101</v>
+        <v>0.4116</v>
       </c>
       <c r="E81" t="n">
-        <v>0.4871000051498413</v>
+        <v>0.4943000078201294</v>
       </c>
       <c r="F81" t="n">
         <v>0.326</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4411</v>
+        <v>0.4433</v>
       </c>
     </row>
     <row r="82">
@@ -2637,19 +2637,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.4602</v>
+        <v>0.4497</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4185</v>
+        <v>0.4225</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4905000030994415</v>
+        <v>0.5011000037193298</v>
       </c>
       <c r="F82" t="n">
         <v>0.27</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4396</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="83">
@@ -2664,19 +2664,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.2184</v>
+        <v>0.2236</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2957</v>
+        <v>0.3169</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2400999963283539</v>
+        <v>0.2721000015735626</v>
       </c>
       <c r="F83" t="n">
         <v>0.2528</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2535</v>
+        <v>0.2724</v>
       </c>
     </row>
     <row r="84">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.2235</v>
+        <v>0.2293</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2951</v>
+        <v>0.311</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2423000037670135</v>
+        <v>0.2721000015735626</v>
       </c>
       <c r="F84" t="n">
         <v>0.2532</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2552</v>
+        <v>0.2714</v>
       </c>
     </row>
     <row r="85">
@@ -2718,19 +2718,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.2196</v>
+        <v>0.2257</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2932</v>
+        <v>0.3128</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2412000000476837</v>
+        <v>0.2712000012397766</v>
       </c>
       <c r="F85" t="n">
         <v>0.256</v>
       </c>
       <c r="G85" t="n">
-        <v>0.2534</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="86">
@@ -2745,19 +2745,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.4412</v>
+        <v>0.4363</v>
       </c>
       <c r="D86" t="n">
-        <v>0.493</v>
+        <v>0.518</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4505000114440918</v>
+        <v>0.4724000096321106</v>
       </c>
       <c r="F86" t="n">
         <v>0.3591</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4617</v>
+        <v>0.4765</v>
       </c>
     </row>
     <row r="87">
@@ -2772,19 +2772,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.4449</v>
+        <v>0.438</v>
       </c>
       <c r="D87" t="n">
-        <v>0.488</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4485999941825867</v>
+        <v>0.4704999923706055</v>
       </c>
       <c r="F87" t="n">
         <v>0.3784</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4616</v>
+        <v>0.4743</v>
       </c>
     </row>
     <row r="88">
@@ -2799,19 +2799,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.4465</v>
+        <v>0.4355</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4848</v>
+        <v>0.5085</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4415000081062317</v>
+        <v>0.4566999971866608</v>
       </c>
       <c r="F88" t="n">
         <v>0.3818</v>
       </c>
       <c r="G88" t="n">
-        <v>0.4589</v>
+        <v>0.4694</v>
       </c>
     </row>
     <row r="89">
@@ -2826,19 +2826,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.4791</v>
+        <v>0.4777</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4876</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5327000021934509</v>
+        <v>0.5493000149726868</v>
       </c>
       <c r="F89" t="n">
         <v>0.1634</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4761</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="90">
@@ -2853,19 +2853,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.4975</v>
+        <v>0.4967</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4869</v>
+        <v>0.5064</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4514000117778778</v>
+        <v>0.4700999855995178</v>
       </c>
       <c r="F90" t="n">
         <v>0.1541</v>
       </c>
       <c r="G90" t="n">
-        <v>0.455</v>
+        <v>0.4673</v>
       </c>
     </row>
     <row r="91">
@@ -2880,19 +2880,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.5575</v>
+        <v>0.5445</v>
       </c>
       <c r="D91" t="n">
-        <v>0.459</v>
+        <v>0.4669</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5090000033378601</v>
+        <v>0.519599974155426</v>
       </c>
       <c r="F91" t="n">
         <v>0.2588</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4844</v>
+        <v>0.4887</v>
       </c>
     </row>
     <row r="92">
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.5125</v>
+        <v>0.5003</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4346</v>
+        <v>0.4381</v>
       </c>
       <c r="E92" t="n">
-        <v>0.494700014591217</v>
+        <v>0.5054000020027161</v>
       </c>
       <c r="F92" t="n">
         <v>0.3624</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4682</v>
+        <v>0.4714</v>
       </c>
     </row>
     <row r="93">
@@ -2934,19 +2934,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.5232</v>
+        <v>0.5052</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4285</v>
+        <v>0.429</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4986999928951263</v>
+        <v>0.5092999935150146</v>
       </c>
       <c r="F93" t="n">
         <v>0.379</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4709</v>
+        <v>0.4718</v>
       </c>
     </row>
     <row r="94">
@@ -2961,19 +2961,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.5202</v>
+        <v>0.5041</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4385</v>
+        <v>0.4419</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4979999959468842</v>
+        <v>0.5085999965667725</v>
       </c>
       <c r="F94" t="n">
         <v>0.3605</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4725</v>
+        <v>0.4748</v>
       </c>
     </row>
     <row r="95">
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.4684</v>
+        <v>0.4596</v>
       </c>
       <c r="D95" t="n">
-        <v>0.6247</v>
+        <v>0.6197</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4431999921798706</v>
+        <v>0.455700010061264</v>
       </c>
       <c r="F95" t="n">
         <v>0.3821</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5228</v>
+        <v>0.5181</v>
       </c>
     </row>
     <row r="96">
@@ -3015,19 +3015,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.4797</v>
+        <v>0.4649</v>
       </c>
       <c r="D96" t="n">
-        <v>0.6458</v>
+        <v>0.638</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4562999904155731</v>
+        <v>0.4717000126838684</v>
       </c>
       <c r="F96" t="n">
         <v>0.4185</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5414</v>
+        <v>0.5351</v>
       </c>
     </row>
     <row r="97">
@@ -3042,19 +3042,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.4376</v>
+        <v>0.428</v>
       </c>
       <c r="D97" t="n">
-        <v>0.6233</v>
+        <v>0.642</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4442000091075897</v>
+        <v>0.4593000113964081</v>
       </c>
       <c r="F97" t="n">
         <v>0.4211</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5185</v>
+        <v>0.5241</v>
       </c>
     </row>
     <row r="98">
@@ -3069,19 +3069,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.4511</v>
+        <v>0.4337</v>
       </c>
       <c r="D98" t="n">
-        <v>0.589</v>
+        <v>0.5867</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4408999979496002</v>
+        <v>0.4573000073432922</v>
       </c>
       <c r="F98" t="n">
         <v>0.3971</v>
       </c>
       <c r="G98" t="n">
-        <v>0.5044</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="99">
@@ -3096,19 +3096,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.451</v>
+        <v>0.4318</v>
       </c>
       <c r="D99" t="n">
-        <v>0.6136</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="E99" t="n">
-        <v>0.4228000044822693</v>
+        <v>0.4379000067710876</v>
       </c>
       <c r="F99" t="n">
         <v>0.3867</v>
       </c>
       <c r="G99" t="n">
-        <v>0.5083</v>
+        <v>0.5029</v>
       </c>
     </row>
     <row r="100">
@@ -3123,19 +3123,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.475</v>
+        <v>0.4568</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6118</v>
       </c>
       <c r="E100" t="n">
-        <v>0.4648999869823456</v>
+        <v>0.4812000095844269</v>
       </c>
       <c r="F100" t="n">
         <v>0.3536</v>
       </c>
       <c r="G100" t="n">
-        <v>0.5283</v>
+        <v>0.5204</v>
       </c>
     </row>
     <row r="101">
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.4335</v>
+        <v>0.4216</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5681</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4311000108718872</v>
+        <v>0.448199987411499</v>
       </c>
       <c r="F101" t="n">
         <v>0.3837</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4874</v>
+        <v>0.4879</v>
       </c>
     </row>
     <row r="102">
@@ -3177,19 +3177,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.4552</v>
+        <v>0.4316</v>
       </c>
       <c r="D102" t="n">
-        <v>0.5077</v>
+        <v>0.535</v>
       </c>
       <c r="E102" t="n">
-        <v>0.483599990606308</v>
+        <v>0.488099992275238</v>
       </c>
       <c r="F102" t="n">
         <v>0.3303</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4786</v>
+        <v>0.4847</v>
       </c>
     </row>
     <row r="103">
@@ -3204,19 +3204,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.3634</v>
+        <v>0.356</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5083</v>
+        <v>0.5137</v>
       </c>
       <c r="E103" t="n">
-        <v>0.4120000004768372</v>
+        <v>0.4221000075340271</v>
       </c>
       <c r="F103" t="n">
         <v>0.379</v>
       </c>
       <c r="G103" t="n">
-        <v>0.4395</v>
+        <v>0.4411</v>
       </c>
     </row>
     <row r="104">
@@ -3231,19 +3231,19 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.3639</v>
+        <v>0.3563</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5391</v>
+        <v>0.5258</v>
       </c>
       <c r="E104" t="n">
-        <v>0.4126999974250793</v>
+        <v>0.4228000044822693</v>
       </c>
       <c r="F104" t="n">
         <v>0.3715</v>
       </c>
       <c r="G104" t="n">
-        <v>0.452</v>
+        <v>0.4454</v>
       </c>
     </row>
     <row r="105">
@@ -3258,19 +3258,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.438</v>
+        <v>0.425</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4556</v>
+        <v>0.4582</v>
       </c>
       <c r="E105" t="n">
-        <v>0.4413000047206879</v>
+        <v>0.4643999934196472</v>
       </c>
       <c r="F105" t="n">
         <v>0.4571</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4512</v>
+        <v>0.4564</v>
       </c>
     </row>
     <row r="106">
@@ -3285,19 +3285,19 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.4627</v>
+        <v>0.4445</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4332</v>
+        <v>0.4223</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4934000074863434</v>
+        <v>0.505299985408783</v>
       </c>
       <c r="F106" t="n">
         <v>0.4109</v>
       </c>
       <c r="G106" t="n">
-        <v>0.4595</v>
+        <v>0.4564</v>
       </c>
     </row>
     <row r="107">
@@ -3312,19 +3312,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.4551</v>
+        <v>0.4378</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4453</v>
+        <v>0.4231</v>
       </c>
       <c r="E107" t="n">
-        <v>0.4954000115394592</v>
+        <v>0.5069000124931335</v>
       </c>
       <c r="F107" t="n">
         <v>0.3713</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4598</v>
+        <v>0.4522</v>
       </c>
     </row>
     <row r="108">
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.4704</v>
+        <v>0.4517</v>
       </c>
       <c r="D108" t="n">
-        <v>0.451</v>
+        <v>0.4348</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4972000122070312</v>
+        <v>0.5087000131607056</v>
       </c>
       <c r="F108" t="n">
         <v>0.3441</v>
       </c>
       <c r="G108" t="n">
-        <v>0.464</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="109">
@@ -3366,19 +3366,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.4415</v>
+        <v>0.4293</v>
       </c>
       <c r="D109" t="n">
-        <v>0.5836</v>
+        <v>0.553</v>
       </c>
       <c r="E109" t="n">
-        <v>0.4429999887943268</v>
+        <v>0.4661000072956085</v>
       </c>
       <c r="F109" t="n">
         <v>0.3534</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4967</v>
+        <v>0.4859</v>
       </c>
     </row>
     <row r="110">
@@ -3393,19 +3393,19 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.4337</v>
+        <v>0.428</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4571</v>
+        <v>0.4755</v>
       </c>
       <c r="E110" t="n">
-        <v>0.4318000078201294</v>
+        <v>0.4537000060081482</v>
       </c>
       <c r="F110" t="n">
         <v>0.2113</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4264</v>
+        <v>0.4387</v>
       </c>
     </row>
     <row r="111">
@@ -3420,19 +3420,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.4407</v>
+        <v>0.4303</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4986</v>
+        <v>0.5132</v>
       </c>
       <c r="E111" t="n">
-        <v>0.4411999881267548</v>
+        <v>0.4474000036716461</v>
       </c>
       <c r="F111" t="n">
         <v>0.3334</v>
       </c>
       <c r="G111" t="n">
-        <v>0.4589</v>
+        <v>0.4626</v>
       </c>
     </row>
     <row r="112">
@@ -3447,19 +3447,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.4449</v>
+        <v>0.4417</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4897</v>
+        <v>0.4998</v>
       </c>
       <c r="E112" t="n">
-        <v>0.4393999874591827</v>
+        <v>0.4424999952316284</v>
       </c>
       <c r="F112" t="n">
         <v>0.3076</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4534</v>
+        <v>0.4562</v>
       </c>
     </row>
     <row r="113">
@@ -3474,19 +3474,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.4832</v>
+        <v>0.4787</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5787</v>
+        <v>0.5675</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4966000020503998</v>
+        <v>0.5009999871253967</v>
       </c>
       <c r="F113" t="n">
         <v>0.243</v>
       </c>
       <c r="G113" t="n">
-        <v>0.511</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="114">
@@ -3501,19 +3501,19 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.4813</v>
+        <v>0.4761</v>
       </c>
       <c r="D114" t="n">
-        <v>0.6024</v>
+        <v>0.5799</v>
       </c>
       <c r="E114" t="n">
-        <v>0.4972000122070312</v>
+        <v>0.5016000270843506</v>
       </c>
       <c r="F114" t="n">
         <v>0.2499</v>
       </c>
       <c r="G114" t="n">
-        <v>0.5212</v>
+        <v>0.5101</v>
       </c>
     </row>
     <row r="115">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.4739</v>
+        <v>0.4809</v>
       </c>
       <c r="D115" t="n">
-        <v>0.5322</v>
+        <v>0.5212</v>
       </c>
       <c r="E115" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5297999978065491</v>
       </c>
       <c r="F115" t="n">
         <v>0.1342</v>
       </c>
       <c r="G115" t="n">
-        <v>0.487</v>
+        <v>0.4874</v>
       </c>
     </row>
     <row r="116">
@@ -3555,19 +3555,19 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.4862</v>
+        <v>0.4743</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4433</v>
+        <v>0.4148</v>
       </c>
       <c r="E116" t="n">
-        <v>0.5404000282287598</v>
+        <v>0.5418999791145325</v>
       </c>
       <c r="F116" t="n">
         <v>0.3055</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4742</v>
+        <v>0.4633</v>
       </c>
     </row>
     <row r="117">
@@ -3582,19 +3582,19 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.4854</v>
+        <v>0.4729</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4834</v>
+        <v>0.4583</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5092999935150146</v>
+        <v>0.5055999755859375</v>
       </c>
       <c r="F117" t="n">
         <v>0.497</v>
       </c>
       <c r="G117" t="n">
-        <v>0.4982</v>
+        <v>0.4848</v>
       </c>
     </row>
     <row r="118">
@@ -3609,19 +3609,19 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.4472</v>
+        <v>0.4409</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4975</v>
+        <v>0.4815</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4542999863624573</v>
+        <v>0.4537999927997589</v>
       </c>
       <c r="F118" t="n">
         <v>0.5698</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4847</v>
+        <v>0.4757</v>
       </c>
     </row>
     <row r="119">
@@ -3636,19 +3636,19 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.4509</v>
+        <v>0.4477</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4858</v>
+        <v>0.4672</v>
       </c>
       <c r="E119" t="n">
-        <v>0.4420999884605408</v>
+        <v>0.4395000040531158</v>
       </c>
       <c r="F119" t="n">
         <v>0.6351</v>
       </c>
       <c r="G119" t="n">
-        <v>0.4828</v>
+        <v>0.4726</v>
       </c>
     </row>
     <row r="120">
@@ -3663,19 +3663,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.4446</v>
+        <v>0.4429</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4848</v>
+        <v>0.4663</v>
       </c>
       <c r="E120" t="n">
-        <v>0.440200001001358</v>
+        <v>0.4395000040531158</v>
       </c>
       <c r="F120" t="n">
         <v>0.5666</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4743</v>
+        <v>0.4652</v>
       </c>
     </row>
     <row r="121">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.4505</v>
+        <v>0.4408</v>
       </c>
       <c r="D121" t="n">
-        <v>0.5924</v>
+        <v>0.6065</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4350000023841858</v>
+        <v>0.4359999895095825</v>
       </c>
       <c r="F121" t="n">
         <v>0.5473</v>
       </c>
       <c r="G121" t="n">
-        <v>0.5171</v>
+        <v>0.5165999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -3717,19 +3717,19 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.2154</v>
+        <v>0.2213</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3325</v>
+        <v>0.2978</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2064999938011169</v>
+        <v>0.2029999941587448</v>
       </c>
       <c r="F122" t="n">
         <v>0.1586</v>
       </c>
       <c r="G122" t="n">
-        <v>0.2497</v>
+        <v>0.2332</v>
       </c>
     </row>
     <row r="123">
@@ -3744,19 +3744,19 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.2163</v>
+        <v>0.2216</v>
       </c>
       <c r="D123" t="n">
-        <v>0.325</v>
+        <v>0.2997</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2116000056266785</v>
+        <v>0.2066999971866608</v>
       </c>
       <c r="F123" t="n">
         <v>0.089</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2422</v>
+        <v>0.2291</v>
       </c>
     </row>
     <row r="124">
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.2124</v>
+        <v>0.2169</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3341</v>
+        <v>0.3088</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2140000015497208</v>
+        <v>0.2144999951124191</v>
       </c>
       <c r="F124" t="n">
         <v>0.1004</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2468</v>
+        <v>0.2352</v>
       </c>
     </row>
     <row r="125">
@@ -3798,19 +3798,19 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.3843</v>
+        <v>0.3799</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4415</v>
+        <v>0.4566</v>
       </c>
       <c r="E125" t="n">
-        <v>0.4034999907016754</v>
+        <v>0.4124999940395355</v>
       </c>
       <c r="F125" t="n">
         <v>0.111</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3907</v>
+        <v>0.3976</v>
       </c>
     </row>
     <row r="126">
@@ -3825,19 +3825,19 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.4001</v>
+        <v>0.3952</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4512</v>
+        <v>0.4663</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4027999937534332</v>
+        <v>0.411300003528595</v>
       </c>
       <c r="F126" t="n">
         <v>0.117</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3988</v>
+        <v>0.4052</v>
       </c>
     </row>
     <row r="127">
@@ -3852,19 +3852,19 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.385</v>
+        <v>0.3803</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4334</v>
+        <v>0.4115</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3738999962806702</v>
+        <v>0.3704999983310699</v>
       </c>
       <c r="F127" t="n">
         <v>0.0824</v>
       </c>
       <c r="G127" t="n">
-        <v>0.3761</v>
+        <v>0.3637</v>
       </c>
     </row>
     <row r="128">
@@ -3879,19 +3879,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.2119</v>
+        <v>0.2148</v>
       </c>
       <c r="D128" t="n">
-        <v>0.344</v>
+        <v>0.3188</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2240000069141388</v>
+        <v>0.2242999970912933</v>
       </c>
       <c r="F128" t="n">
         <v>0.0324</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2478</v>
+        <v>0.2358</v>
       </c>
     </row>
     <row r="129">
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.206</v>
+        <v>0.2037</v>
       </c>
       <c r="D129" t="n">
-        <v>0.3527</v>
+        <v>0.3366</v>
       </c>
       <c r="E129" t="n">
-        <v>0.2157000005245209</v>
+        <v>0.2160000056028366</v>
       </c>
       <c r="F129" t="n">
         <v>0.1135</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2546</v>
+        <v>0.2445</v>
       </c>
     </row>
     <row r="130">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.2163</v>
+        <v>0.2168</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3782</v>
+        <v>0.3819</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2520999908447266</v>
+        <v>0.26460000872612</v>
       </c>
       <c r="F130" t="n">
         <v>0.1035</v>
       </c>
       <c r="G130" t="n">
-        <v>0.2778</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="131">
@@ -3960,19 +3960,19 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.2174</v>
+        <v>0.2178</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3815</v>
+        <v>0.3851</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2508000135421753</v>
+        <v>0.263700008392334</v>
       </c>
       <c r="F131" t="n">
         <v>0.0434</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2737</v>
+        <v>0.2765</v>
       </c>
     </row>
     <row r="132">
@@ -3987,19 +3987,19 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.2119</v>
+        <v>0.2133</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3828</v>
+        <v>0.3857</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2565999925136566</v>
+        <v>0.2694999873638153</v>
       </c>
       <c r="F132" t="n">
         <v>0.0211</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2727</v>
+        <v>0.2756</v>
       </c>
     </row>
     <row r="133">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.2254</v>
+        <v>0.2298</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3502</v>
+        <v>0.3273</v>
       </c>
       <c r="E133" t="n">
-        <v>0.2419999986886978</v>
+        <v>0.2432000041007996</v>
       </c>
       <c r="F133" t="n">
         <v>0.0347</v>
       </c>
       <c r="G133" t="n">
-        <v>0.2593</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="134">
@@ -4041,19 +4041,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.3694</v>
+        <v>0.3663</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4509</v>
+        <v>0.4213</v>
       </c>
       <c r="E134" t="n">
-        <v>0.385699987411499</v>
+        <v>0.3873000144958496</v>
       </c>
       <c r="F134" t="n">
         <v>0.0892</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3837</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="135">
@@ -4068,19 +4068,19 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.3691</v>
+        <v>0.3624</v>
       </c>
       <c r="D135" t="n">
-        <v>0.426</v>
+        <v>0.4057</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3795000016689301</v>
+        <v>0.3806999921798706</v>
       </c>
       <c r="F135" t="n">
         <v>0.1385</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3758</v>
+        <v>0.3655</v>
       </c>
     </row>
     <row r="136">
@@ -4095,19 +4095,19 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.369</v>
+        <v>0.3645</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4268</v>
+        <v>0.4075</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3858999907970428</v>
+        <v>0.3871000111103058</v>
       </c>
       <c r="F136" t="n">
         <v>0.1749</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3812</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="137">
@@ -4122,19 +4122,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.3345</v>
+        <v>0.3359</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4005</v>
+        <v>0.3794</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3714999854564667</v>
+        <v>0.3777999877929688</v>
       </c>
       <c r="F137" t="n">
         <v>0.1176</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3526</v>
+        <v>0.3462</v>
       </c>
     </row>
     <row r="138">
@@ -4149,19 +4149,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.2385</v>
+        <v>0.2425</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3804</v>
+        <v>0.3806</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2892000079154968</v>
+        <v>0.2949000000953674</v>
       </c>
       <c r="F138" t="n">
         <v>0.1031</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2952</v>
+        <v>0.2961</v>
       </c>
     </row>
     <row r="139">
@@ -4176,19 +4176,19 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.3993</v>
+        <v>0.3996</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4649</v>
+        <v>0.4659</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4273000061511993</v>
+        <v>0.4402999877929688</v>
       </c>
       <c r="F139" t="n">
         <v>0.1701</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4164</v>
+        <v>0.4203</v>
       </c>
     </row>
     <row r="140">
@@ -4203,19 +4203,19 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.3125</v>
+        <v>0.3116</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4002</v>
+        <v>0.3795</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3806000053882599</v>
+        <v>0.3930999934673309</v>
       </c>
       <c r="F140" t="n">
         <v>0.2328</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3601</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="141">
@@ -4230,19 +4230,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.3202</v>
+        <v>0.3178</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4063</v>
+        <v>0.3811</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3804999887943268</v>
+        <v>0.3930000066757202</v>
       </c>
       <c r="F141" t="n">
         <v>0.2831</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3688</v>
+        <v>0.3622</v>
       </c>
     </row>
     <row r="142">
@@ -4257,19 +4257,19 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.3161</v>
+        <v>0.3158</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3556</v>
+        <v>0.3323</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3450999855995178</v>
+        <v>0.3407000005245209</v>
       </c>
       <c r="F142" t="n">
         <v>0.2701</v>
       </c>
       <c r="G142" t="n">
-        <v>0.335</v>
+        <v>0.3243</v>
       </c>
     </row>
     <row r="143">
@@ -4284,19 +4284,19 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.2106</v>
+        <v>0.2102</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3311</v>
+        <v>0.3225</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2325000017881393</v>
+        <v>0.2269999980926514</v>
       </c>
       <c r="F143" t="n">
         <v>0.2816</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2666</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="144">
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.3753</v>
+        <v>0.3694</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4129</v>
+        <v>0.3986</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3794000148773193</v>
+        <v>0.3806000053882599</v>
       </c>
       <c r="F144" t="n">
         <v>0.33</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3887</v>
+        <v>0.3812</v>
       </c>
     </row>
     <row r="145">
@@ -4338,19 +4338,19 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.3779</v>
+        <v>0.3725</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4345</v>
+        <v>0.4164</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3862000107765198</v>
+        <v>0.3880999982357025</v>
       </c>
       <c r="F145" t="n">
         <v>0.2567</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3938</v>
+        <v>0.3849</v>
       </c>
     </row>
     <row r="146">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.2299</v>
+        <v>0.2318</v>
       </c>
       <c r="D146" t="n">
         <v>0.2664</v>
@@ -4377,7 +4377,7 @@
         <v>0.1537</v>
       </c>
       <c r="G146" t="n">
-        <v>0.2503</v>
+        <v>0.2517</v>
       </c>
     </row>
     <row r="147">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.2232</v>
+        <v>0.2248</v>
       </c>
       <c r="D147" t="n">
         <v>0.2706</v>
@@ -4404,7 +4404,7 @@
         <v>0.2373</v>
       </c>
       <c r="G147" t="n">
-        <v>0.2309</v>
+        <v>0.2294</v>
       </c>
     </row>
     <row r="148">
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.2437</v>
+        <v>0.2461</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2938</v>
+        <v>0.2906</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2113000005483627</v>
+        <v>0.238999992609024</v>
       </c>
       <c r="F148" t="n">
         <v>0.3305</v>
       </c>
       <c r="G148" t="n">
-        <v>0.257</v>
+        <v>0.2632</v>
       </c>
     </row>
     <row r="149">
@@ -4446,19 +4446,19 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.2264</v>
+        <v>0.2289</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2683</v>
+        <v>0.2695</v>
       </c>
       <c r="E149" t="n">
-        <v>0.2161000072956085</v>
+        <v>0.2437999993562698</v>
       </c>
       <c r="F149" t="n">
         <v>0.2903</v>
       </c>
       <c r="G149" t="n">
-        <v>0.2402</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="150">
@@ -4473,19 +4473,19 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.2233</v>
+        <v>0.2252</v>
       </c>
       <c r="D150" t="n">
         <v>0.2657</v>
       </c>
       <c r="E150" t="n">
-        <v>0.2158000022172928</v>
+        <v>0.2433999925851822</v>
       </c>
       <c r="F150" t="n">
         <v>0.2986</v>
       </c>
       <c r="G150" t="n">
-        <v>0.239</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="151">
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.2269</v>
+        <v>0.2284</v>
       </c>
       <c r="D151" t="n">
         <v>0.2764</v>
       </c>
       <c r="E151" t="n">
-        <v>0.2215999960899353</v>
+        <v>0.2492000013589859</v>
       </c>
       <c r="F151" t="n">
         <v>0.3297</v>
       </c>
       <c r="G151" t="n">
-        <v>0.2488</v>
+        <v>0.2568</v>
       </c>
     </row>
     <row r="152">
@@ -4527,19 +4527,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.2246</v>
+        <v>0.226</v>
       </c>
       <c r="D152" t="n">
         <v>0.2817</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2393999993801117</v>
+        <v>0.2669999897480011</v>
       </c>
       <c r="F152" t="n">
         <v>0.3348</v>
       </c>
       <c r="G152" t="n">
-        <v>0.2562</v>
+        <v>0.2647</v>
       </c>
     </row>
     <row r="153">
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.3694</v>
+        <v>0.3701</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3506</v>
+        <v>0.3615</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4323999881744385</v>
+        <v>0.4833999872207642</v>
       </c>
       <c r="F153" t="n">
         <v>0.4423</v>
       </c>
       <c r="G153" t="n">
-        <v>0.3872</v>
+        <v>0.4108</v>
       </c>
     </row>
     <row r="154">
@@ -4581,19 +4581,19 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.3706</v>
+        <v>0.3737</v>
       </c>
       <c r="D154" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="E154" t="n">
-        <v>0.4345000088214874</v>
+        <v>0.4848999977111816</v>
       </c>
       <c r="F154" t="n">
         <v>0.4372</v>
       </c>
       <c r="G154" t="n">
-        <v>0.399</v>
+        <v>0.4224</v>
       </c>
     </row>
     <row r="155">
@@ -4608,19 +4608,19 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.3722</v>
+        <v>0.3719</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3603</v>
+        <v>0.3597</v>
       </c>
       <c r="E155" t="n">
-        <v>0.4462999999523163</v>
+        <v>0.4494999945163727</v>
       </c>
       <c r="F155" t="n">
         <v>0.4049</v>
       </c>
       <c r="G155" t="n">
-        <v>0.3928</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="156">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.2395</v>
+        <v>0.2406</v>
       </c>
       <c r="D156" t="n">
         <v>0.2812</v>
@@ -4647,7 +4647,7 @@
         <v>0.3532</v>
       </c>
       <c r="G156" t="n">
-        <v>0.2611</v>
+        <v>0.2602</v>
       </c>
     </row>
     <row r="157">
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.2688</v>
+        <v>0.27</v>
       </c>
       <c r="D157" t="n">
         <v>0.2958</v>
@@ -4674,7 +4674,7 @@
         <v>0.1913</v>
       </c>
       <c r="G157" t="n">
-        <v>0.2628</v>
+        <v>0.2617</v>
       </c>
     </row>
     <row r="158">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.3027</v>
+        <v>0.3009</v>
       </c>
       <c r="D158" t="n">
-        <v>0.288</v>
+        <v>0.2872</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3264999985694885</v>
+        <v>0.3251999914646149</v>
       </c>
       <c r="F158" t="n">
         <v>0.4207</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3114</v>
+        <v>0.3112</v>
       </c>
     </row>
     <row r="159">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.3043</v>
+        <v>0.3006</v>
       </c>
       <c r="D159" t="n">
-        <v>0.289</v>
+        <v>0.2881</v>
       </c>
       <c r="E159" t="n">
         <v>0.3235999941825867</v>
@@ -4728,7 +4728,7 @@
         <v>0.4377</v>
       </c>
       <c r="G159" t="n">
-        <v>0.3128</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="160">
@@ -4743,19 +4743,19 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.3012</v>
+        <v>0.2981</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2929</v>
+        <v>0.3036</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3122000098228455</v>
+        <v>0.3384999930858612</v>
       </c>
       <c r="F160" t="n">
         <v>0.4399</v>
       </c>
       <c r="G160" t="n">
-        <v>0.3104</v>
+        <v>0.3231</v>
       </c>
     </row>
     <row r="161">
@@ -4770,19 +4770,19 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.2604</v>
+        <v>0.2576</v>
       </c>
       <c r="D161" t="n">
-        <v>0.3218</v>
+        <v>0.3186</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2365999966859818</v>
+        <v>0.2642000019550323</v>
       </c>
       <c r="F161" t="n">
         <v>0.3935</v>
       </c>
       <c r="G161" t="n">
-        <v>0.2858</v>
+        <v>0.2907</v>
       </c>
     </row>
     <row r="162">
@@ -4800,7 +4800,7 @@
         <v>0.255</v>
       </c>
       <c r="D162" t="n">
-        <v>0.322</v>
+        <v>0.3188</v>
       </c>
       <c r="E162" t="n">
         <v>0.2345000058412552</v>
@@ -4809,7 +4809,7 @@
         <v>0.2913</v>
       </c>
       <c r="G162" t="n">
-        <v>0.275</v>
+        <v>0.2714</v>
       </c>
     </row>
     <row r="163">
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.2513</v>
+        <v>0.2507</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3177</v>
+        <v>0.3145</v>
       </c>
       <c r="E163" t="n">
         <v>0.2433000057935715</v>
@@ -4836,7 +4836,7 @@
         <v>0.2939</v>
       </c>
       <c r="G163" t="n">
-        <v>0.2752</v>
+        <v>0.2718</v>
       </c>
     </row>
     <row r="164">
@@ -4851,19 +4851,19 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.2562</v>
+        <v>0.2539</v>
       </c>
       <c r="D164" t="n">
-        <v>0.3137</v>
+        <v>0.3105</v>
       </c>
       <c r="E164" t="n">
-        <v>0.2335000038146973</v>
+        <v>0.2328999936580658</v>
       </c>
       <c r="F164" t="n">
         <v>0.4201</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2829</v>
+        <v>0.2787</v>
       </c>
     </row>
     <row r="165">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.3069</v>
+        <v>0.2998</v>
       </c>
       <c r="D165" t="n">
-        <v>0.2966</v>
+        <v>0.2936</v>
       </c>
       <c r="E165" t="n">
         <v>0.3133000135421753</v>
@@ -4890,7 +4890,7 @@
         <v>0.5296</v>
       </c>
       <c r="G165" t="n">
-        <v>0.3216</v>
+        <v>0.3191</v>
       </c>
     </row>
     <row r="166">
@@ -4905,19 +4905,19 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.3111</v>
+        <v>0.3053</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2932</v>
+        <v>0.2922</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3217999935150146</v>
+        <v>0.3224000036716461</v>
       </c>
       <c r="F166" t="n">
         <v>0.5691000000000001</v>
       </c>
       <c r="G166" t="n">
-        <v>0.3272</v>
+        <v>0.3263</v>
       </c>
     </row>
     <row r="167">
@@ -4932,19 +4932,19 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.3569</v>
+        <v>0.3528</v>
       </c>
       <c r="D167" t="n">
         <v>0.3289</v>
       </c>
       <c r="E167" t="n">
-        <v>0.369700014591217</v>
+        <v>0.3684000074863434</v>
       </c>
       <c r="F167" t="n">
         <v>0.5797</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3684</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="168">
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.3684</v>
+        <v>0.3645</v>
       </c>
       <c r="D168" t="n">
         <v>0.3508</v>
       </c>
       <c r="E168" t="n">
-        <v>0.4185999929904938</v>
+        <v>0.4216000139713287</v>
       </c>
       <c r="F168" t="n">
         <v>0.5982</v>
       </c>
       <c r="G168" t="n">
-        <v>0.3965</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="169">
@@ -4986,19 +4986,19 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.3489</v>
+        <v>0.3477</v>
       </c>
       <c r="D169" t="n">
-        <v>0.304</v>
+        <v>0.3032</v>
       </c>
       <c r="E169" t="n">
-        <v>0.4138999879360199</v>
+        <v>0.4169999957084656</v>
       </c>
       <c r="F169" t="n">
         <v>0.5189</v>
       </c>
       <c r="G169" t="n">
-        <v>0.3641</v>
+        <v>0.3675</v>
       </c>
     </row>
     <row r="170">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.2683</v>
+        <v>0.2703</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3057</v>
+        <v>0.3025</v>
       </c>
       <c r="E170" t="n">
         <v>0.2465000003576279</v>
@@ -5025,7 +5025,7 @@
         <v>0.2102</v>
       </c>
       <c r="G170" t="n">
-        <v>0.2679</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="171">
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.2808</v>
+        <v>0.283</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3072</v>
+        <v>0.304</v>
       </c>
       <c r="E171" t="n">
         <v>0.3120999932289124</v>
@@ -5052,7 +5052,7 @@
         <v>0.1988</v>
       </c>
       <c r="G171" t="n">
-        <v>0.2902</v>
+        <v>0.2897</v>
       </c>
     </row>
     <row r="172">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.261</v>
+        <v>0.2619</v>
       </c>
       <c r="D172" t="n">
-        <v>0.3047</v>
+        <v>0.3015</v>
       </c>
       <c r="E172" t="n">
         <v>0.2432000041007996</v>
@@ -5079,7 +5079,7 @@
         <v>0.2141</v>
       </c>
       <c r="G172" t="n">
-        <v>0.265</v>
+        <v>0.2623</v>
       </c>
     </row>
     <row r="173">
@@ -5094,19 +5094,19 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.2798</v>
+        <v>0.2812</v>
       </c>
       <c r="D173" t="n">
-        <v>0.3084</v>
+        <v>0.3052</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3106000125408173</v>
+        <v>0.3382000029087067</v>
       </c>
       <c r="F173" t="n">
         <v>0.2086</v>
       </c>
       <c r="G173" t="n">
-        <v>0.2909</v>
+        <v>0.2993</v>
       </c>
     </row>
     <row r="174">
@@ -5121,19 +5121,19 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.2702</v>
+        <v>0.2722</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2893</v>
+        <v>0.3008</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2378000020980835</v>
+        <v>0.2630000114440918</v>
       </c>
       <c r="F174" t="n">
         <v>0.3014</v>
       </c>
       <c r="G174" t="n">
-        <v>0.2669</v>
+        <v>0.2787</v>
       </c>
     </row>
     <row r="175">
@@ -5148,19 +5148,19 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.3674</v>
+        <v>0.3664</v>
       </c>
       <c r="D175" t="n">
-        <v>0.3284</v>
+        <v>0.3237</v>
       </c>
       <c r="E175" t="n">
-        <v>0.4081000089645386</v>
+        <v>0.4357999861240387</v>
       </c>
       <c r="F175" t="n">
         <v>0.3929</v>
       </c>
       <c r="G175" t="n">
-        <v>0.3658</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="176">
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.3675</v>
+        <v>0.3669</v>
       </c>
       <c r="D176" t="n">
-        <v>0.3339</v>
+        <v>0.3423</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3977999985218048</v>
+        <v>0.4253999888896942</v>
       </c>
       <c r="F176" t="n">
         <v>0.4031</v>
       </c>
       <c r="G176" t="n">
-        <v>0.3659</v>
+        <v>0.3798</v>
       </c>
     </row>
     <row r="177">
@@ -5202,19 +5202,19 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0.3858</v>
+        <v>0.3804</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3521</v>
+        <v>0.3548</v>
       </c>
       <c r="E177" t="n">
-        <v>0.4025999903678894</v>
+        <v>0.4309999942779541</v>
       </c>
       <c r="F177" t="n">
         <v>0.4842</v>
       </c>
       <c r="G177" t="n">
-        <v>0.3865</v>
+        <v>0.3969</v>
       </c>
     </row>
     <row r="178">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.3707</v>
+        <v>0.3712</v>
       </c>
       <c r="D178" t="n">
         <v>0.3532</v>
@@ -5241,7 +5241,7 @@
         <v>0.346</v>
       </c>
       <c r="G178" t="n">
-        <v>0.3793</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="179">
@@ -5256,19 +5256,19 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.3459</v>
+        <v>0.3457</v>
       </c>
       <c r="D179" t="n">
         <v>0.3336</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4023000001907349</v>
+        <v>0.4101999998092651</v>
       </c>
       <c r="F179" t="n">
         <v>0.108</v>
       </c>
       <c r="G179" t="n">
-        <v>0.336</v>
+        <v>0.3405</v>
       </c>
     </row>
     <row r="180">
@@ -5283,19 +5283,19 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.3031</v>
+        <v>0.3043</v>
       </c>
       <c r="D180" t="n">
         <v>0.3041</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3181999921798706</v>
+        <v>0.3158000111579895</v>
       </c>
       <c r="F180" t="n">
         <v>0.0514</v>
       </c>
       <c r="G180" t="n">
-        <v>0.2832</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="181">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.3043</v>
+        <v>0.3047</v>
       </c>
       <c r="D181" t="n">
         <v>0.2939</v>
@@ -5322,7 +5322,7 @@
         <v>0.1025</v>
       </c>
       <c r="G181" t="n">
-        <v>0.2814</v>
+        <v>0.2819</v>
       </c>
     </row>
     <row r="182">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.2728</v>
+        <v>0.2721</v>
       </c>
       <c r="D182" t="n">
         <v>0.2948</v>
@@ -5349,7 +5349,7 @@
         <v>0.112</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2572</v>
+        <v>0.2557</v>
       </c>
     </row>
     <row r="183">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.2755</v>
+        <v>0.2762</v>
       </c>
       <c r="D183" t="n">
         <v>0.2925</v>
@@ -5376,7 +5376,7 @@
         <v>0.1233</v>
       </c>
       <c r="G183" t="n">
-        <v>0.2567</v>
+        <v>0.2555</v>
       </c>
     </row>
     <row r="184">
@@ -5391,19 +5391,19 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.2767</v>
+        <v>0.2774</v>
       </c>
       <c r="D184" t="n">
         <v>0.2932</v>
       </c>
       <c r="E184" t="n">
-        <v>0.2694999873638153</v>
+        <v>0.269899994134903</v>
       </c>
       <c r="F184" t="n">
         <v>0.1341</v>
       </c>
       <c r="G184" t="n">
-        <v>0.2649</v>
+        <v>0.2645</v>
       </c>
     </row>
     <row r="185">
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.2721</v>
+        <v>0.2742</v>
       </c>
       <c r="D185" t="n">
         <v>0.2695</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2367</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="186">
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.2721</v>
+        <v>0.2739</v>
       </c>
       <c r="D186" t="n">
         <v>0.268</v>
@@ -5457,7 +5457,7 @@
         <v>0.0362</v>
       </c>
       <c r="G186" t="n">
-        <v>0.2392</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="187">
@@ -5472,19 +5472,19 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.3767</v>
+        <v>0.37</v>
       </c>
       <c r="D187" t="n">
         <v>0.3058</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4291000068187714</v>
+        <v>0.4575999975204468</v>
       </c>
       <c r="F187" t="n">
         <v>0.2807</v>
       </c>
       <c r="G187" t="n">
-        <v>0.3551</v>
+        <v>0.3663</v>
       </c>
     </row>
     <row r="188">
@@ -5499,19 +5499,19 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.3627</v>
+        <v>0.3572</v>
       </c>
       <c r="D188" t="n">
-        <v>0.335</v>
+        <v>0.3344</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4336999952793121</v>
+        <v>0.431300014257431</v>
       </c>
       <c r="F188" t="n">
         <v>0.2231</v>
       </c>
       <c r="G188" t="n">
-        <v>0.3602</v>
+        <v>0.3606</v>
       </c>
     </row>
     <row r="189">
@@ -5526,19 +5526,19 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.553</v>
+        <v>0.5332</v>
       </c>
       <c r="D189" t="n">
-        <v>0.5241</v>
+        <v>0.5131</v>
       </c>
       <c r="E189" t="n">
-        <v>0.5178999900817871</v>
+        <v>0.5336999893188477</v>
       </c>
       <c r="F189" t="n">
         <v>0.3133</v>
       </c>
       <c r="G189" t="n">
-        <v>0.5178</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.3697</v>
+        <v>0.3667</v>
       </c>
       <c r="D190" t="n">
         <v>0.3591</v>
@@ -5565,7 +5565,7 @@
         <v>0.0065</v>
       </c>
       <c r="G190" t="n">
-        <v>0.3554</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="191">
@@ -5580,19 +5580,19 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.3189</v>
+        <v>0.3202</v>
       </c>
       <c r="D191" t="n">
         <v>0.3396</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3704000115394592</v>
+        <v>0.3704999983310699</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.3042</v>
+        <v>0.3056</v>
       </c>
     </row>
     <row r="192">
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.3189</v>
+        <v>0.3174</v>
       </c>
       <c r="D192" t="n">
         <v>0.275</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3337000012397766</v>
+        <v>0.3339000046253204</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.2612</v>
+        <v>0.2624</v>
       </c>
     </row>
     <row r="193">
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.3167</v>
+        <v>0.3139</v>
       </c>
       <c r="D193" t="n">
         <v>0.3128</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3346000015735626</v>
+        <v>0.3346999883651733</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -5661,19 +5661,19 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.3436</v>
+        <v>0.3416</v>
       </c>
       <c r="D194" t="n">
         <v>0.3394</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3418999910354614</v>
+        <v>0.3458999991416931</v>
       </c>
       <c r="F194" t="n">
         <v>0.0124</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3113</v>
+        <v>0.3121</v>
       </c>
     </row>
     <row r="195">
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.339</v>
+        <v>0.336</v>
       </c>
       <c r="D195" t="n">
         <v>0.3345</v>
       </c>
       <c r="E195" t="n">
-        <v>0.3267999887466431</v>
+        <v>0.3296999931335449</v>
       </c>
       <c r="F195" t="n">
         <v>0.0212</v>
       </c>
       <c r="G195" t="n">
-        <v>0.3044</v>
+        <v>0.3043</v>
       </c>
     </row>
     <row r="196">
@@ -5715,19 +5715,19 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.3433</v>
+        <v>0.3388</v>
       </c>
       <c r="D196" t="n">
         <v>0.3358</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3095999956130981</v>
+        <v>0.3084999918937683</v>
       </c>
       <c r="F196" t="n">
         <v>0.0521</v>
       </c>
       <c r="G196" t="n">
-        <v>0.3035</v>
+        <v>0.3012</v>
       </c>
     </row>
     <row r="197">
@@ -5742,19 +5742,19 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.3447</v>
+        <v>0.3449</v>
       </c>
       <c r="D197" t="n">
         <v>0.3094</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3786999881267548</v>
+        <v>0.363400012254715</v>
       </c>
       <c r="F197" t="n">
         <v>0.0665</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3149</v>
+        <v>0.3117</v>
       </c>
     </row>
     <row r="198">
@@ -5769,19 +5769,19 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.3386</v>
+        <v>0.3465</v>
       </c>
       <c r="D198" t="n">
         <v>0.3065</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3456999957561493</v>
+        <v>0.3449000120162964</v>
       </c>
       <c r="F198" t="n">
         <v>0.0271</v>
       </c>
       <c r="G198" t="n">
-        <v>0.2988</v>
+        <v>0.3014</v>
       </c>
     </row>
     <row r="199">
@@ -5796,19 +5796,19 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.4894</v>
+        <v>0.4895</v>
       </c>
       <c r="D199" t="n">
-        <v>0.6146</v>
+        <v>0.6177</v>
       </c>
       <c r="E199" t="n">
-        <v>0.5288000106811523</v>
+        <v>0.5317000150680542</v>
       </c>
       <c r="F199" t="n">
         <v>0.1541</v>
       </c>
       <c r="G199" t="n">
-        <v>0.5293</v>
+        <v>0.5295</v>
       </c>
     </row>
     <row r="200">
@@ -5823,19 +5823,19 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.676</v>
+        <v>0.658</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4947</v>
+        <v>0.5285</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5351999998092651</v>
+        <v>0.5358999967575073</v>
       </c>
       <c r="F200" t="n">
         <v>0.2257</v>
       </c>
       <c r="G200" t="n">
-        <v>0.5327</v>
+        <v>0.5419</v>
       </c>
     </row>
     <row r="201">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.6758</v>
+        <v>0.6728</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5363</v>
+        <v>0.57</v>
       </c>
       <c r="E201" t="n">
-        <v>0.6119999885559082</v>
+        <v>0.6136000156402588</v>
       </c>
       <c r="F201" t="n">
         <v>0.2387</v>
       </c>
       <c r="G201" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5884</v>
       </c>
     </row>
     <row r="202">
@@ -5877,19 +5877,19 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.366</v>
+        <v>0.3667</v>
       </c>
       <c r="D202" t="n">
         <v>0.4233</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4481000006198883</v>
+        <v>0.4492999911308289</v>
       </c>
       <c r="F202" t="n">
         <v>0.1469</v>
       </c>
       <c r="G202" t="n">
-        <v>0.3953</v>
+        <v>0.3968</v>
       </c>
     </row>
     <row r="203">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.3458</v>
+        <v>0.3498</v>
       </c>
       <c r="D203" t="n">
         <v>0.4136</v>
@@ -5916,7 +5916,7 @@
         <v>0.1105</v>
       </c>
       <c r="G203" t="n">
-        <v>0.3857</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="204">
@@ -5931,19 +5931,19 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>0.2957</v>
+        <v>0.296</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3326</v>
+        <v>0.3358</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3389999866485596</v>
+        <v>0.3429999947547913</v>
       </c>
       <c r="F204" t="n">
         <v>0.0736</v>
       </c>
       <c r="G204" t="n">
-        <v>0.3014</v>
+        <v>0.3045</v>
       </c>
     </row>
     <row r="205">
@@ -5958,19 +5958,19 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.2921</v>
+        <v>0.2936</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3382</v>
+        <v>0.3414</v>
       </c>
       <c r="E205" t="n">
-        <v>0.3377000093460083</v>
+        <v>0.3416999876499176</v>
       </c>
       <c r="F205" t="n">
         <v>0.0604</v>
       </c>
       <c r="G205" t="n">
-        <v>0.3013</v>
+        <v>0.3045</v>
       </c>
     </row>
     <row r="206">
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.2531</v>
+        <v>0.248</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3235</v>
+        <v>0.3146</v>
       </c>
       <c r="E206" t="n">
         <v>0.2779999971389771</v>
@@ -5997,7 +5997,7 @@
         <v>0.1334</v>
       </c>
       <c r="G206" t="n">
-        <v>0.2743</v>
+        <v>0.2686</v>
       </c>
     </row>
     <row r="207">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.2514</v>
+        <v>0.2438</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3211</v>
+        <v>0.3121</v>
       </c>
       <c r="E207" t="n">
         <v>0.2655999958515167</v>
@@ -6024,7 +6024,7 @@
         <v>0.1529</v>
       </c>
       <c r="G207" t="n">
-        <v>0.2709</v>
+        <v>0.2643</v>
       </c>
     </row>
     <row r="208">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.2418</v>
+        <v>0.2379</v>
       </c>
       <c r="D208" t="n">
-        <v>0.3213</v>
+        <v>0.3124</v>
       </c>
       <c r="E208" t="n">
         <v>0.2709999978542328</v>
@@ -6051,7 +6051,7 @@
         <v>0.1545</v>
       </c>
       <c r="G208" t="n">
-        <v>0.2705</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="209">
@@ -6066,19 +6066,19 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.2613</v>
+        <v>0.2636</v>
       </c>
       <c r="D209" t="n">
-        <v>0.2903</v>
+        <v>0.2699</v>
       </c>
       <c r="E209" t="n">
-        <v>0.2766999900341034</v>
+        <v>0.2755999863147736</v>
       </c>
       <c r="F209" t="n">
         <v>0.1901</v>
       </c>
       <c r="G209" t="n">
-        <v>0.2671</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="210">
@@ -6093,19 +6093,19 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.2741</v>
+        <v>0.2726</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2973</v>
+        <v>0.2879</v>
       </c>
       <c r="E210" t="n">
-        <v>0.2845999896526337</v>
+        <v>0.2834999859333038</v>
       </c>
       <c r="F210" t="n">
         <v>0.1167</v>
       </c>
       <c r="G210" t="n">
-        <v>0.269</v>
+        <v>0.2644</v>
       </c>
     </row>
     <row r="211">
@@ -6120,19 +6120,19 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.2516</v>
+        <v>0.2527</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3061</v>
+        <v>0.3263</v>
       </c>
       <c r="E211" t="n">
-        <v>0.2331999987363815</v>
+        <v>0.2325000017881393</v>
       </c>
       <c r="F211" t="n">
         <v>0.1335</v>
       </c>
       <c r="G211" t="n">
-        <v>0.2533</v>
+        <v>0.2593</v>
       </c>
     </row>
     <row r="212">
@@ -6147,19 +6147,19 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.24</v>
+        <v>0.2422</v>
       </c>
       <c r="D212" t="n">
-        <v>0.3</v>
+        <v>0.3091</v>
       </c>
       <c r="E212" t="n">
-        <v>0.2310999929904938</v>
+        <v>0.2300000041723251</v>
       </c>
       <c r="F212" t="n">
         <v>0.097</v>
       </c>
       <c r="G212" t="n">
-        <v>0.2441</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="213">
@@ -6174,19 +6174,19 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.2411</v>
+        <v>0.238</v>
       </c>
       <c r="D213" t="n">
-        <v>0.3478</v>
+        <v>0.3388</v>
       </c>
       <c r="E213" t="n">
-        <v>0.2506999969482422</v>
+        <v>0.2494000047445297</v>
       </c>
       <c r="F213" t="n">
         <v>0.054</v>
       </c>
       <c r="G213" t="n">
-        <v>0.2663</v>
+        <v>0.2593</v>
       </c>
     </row>
     <row r="214">
@@ -6201,19 +6201,19 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.2374</v>
+        <v>0.2285</v>
       </c>
       <c r="D214" t="n">
-        <v>0.3404</v>
+        <v>0.3317</v>
       </c>
       <c r="E214" t="n">
-        <v>0.2612000107765198</v>
+        <v>0.2599999904632568</v>
       </c>
       <c r="F214" t="n">
         <v>0.1963</v>
       </c>
       <c r="G214" t="n">
-        <v>0.2781</v>
+        <v>0.2703</v>
       </c>
     </row>
     <row r="215">
@@ -6228,19 +6228,19 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.6865</v>
+        <v>0.6866</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5743</v>
+        <v>0.6038</v>
       </c>
       <c r="E215" t="n">
-        <v>0.5963000059127808</v>
+        <v>0.5881000161170959</v>
       </c>
       <c r="F215" t="n">
         <v>0.3752</v>
       </c>
       <c r="G215" t="n">
-        <v>0.5998</v>
+        <v>0.6084000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.2619</v>
+        <v>0.2552</v>
       </c>
       <c r="D216" t="n">
-        <v>0.2905</v>
+        <v>0.2835</v>
       </c>
       <c r="E216" t="n">
         <v>0.2879999876022339</v>
@@ -6267,7 +6267,7 @@
         <v>0.2798</v>
       </c>
       <c r="G216" t="n">
-        <v>0.2786</v>
+        <v>0.2743</v>
       </c>
     </row>
     <row r="217">
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.2213</v>
+        <v>0.2149</v>
       </c>
       <c r="D217" t="n">
-        <v>0.2953</v>
+        <v>0.2949</v>
       </c>
       <c r="E217" t="n">
         <v>0.2373999953269958</v>
@@ -6294,7 +6294,7 @@
         <v>0.2861</v>
       </c>
       <c r="G217" t="n">
-        <v>0.2562</v>
+        <v>0.2532</v>
       </c>
     </row>
   </sheetData>
